--- a/libs/porting-tasks-template.xlsx
+++ b/libs/porting-tasks-template.xlsx
@@ -818,7 +818,7 @@
         <t>记录设备测试或 binary 测试结果</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>记录失败阶段、失败原因或补充说明</t>
       </text>
@@ -1115,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1126,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -1172,6 +1172,11 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>HAP测试状态（待处理/pass/fail/skip）</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>失败原因/备注</t>
         </is>
       </c>
